--- a/DataTables/DetailText/剧情/022_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/022_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CB0DF2-8213-41AE-A50F-05A13BD5A8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702BBFB9-2329-416C-AA10-F80776A61898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
   <si>
     <t>StoryID</t>
   </si>
@@ -142,11 +142,41 @@
     <t>story_npc_cured</t>
   </si>
   <si>
-    <t>008_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>性空</t>
+    <r>
+      <t>022治</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>成功</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>022_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>022_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>柳敬亭</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -154,103 +184,332 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>师</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>傅所患的乃是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>肾精不足之症，嗯…是房事过劳所致…</t>
-    </r>
-    <rPh sb="1" eb="2">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ショ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>マト</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ゼ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>セイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ブソク</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟，施主啊，这可不敢乱说啊，我可是出家人啊，怎么会干那种事呢。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>…</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>一定是我晚上念经太过用功，着凉了。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>是是是，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>师</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>傅</t>
+    <t>哎呀，舒服多了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>您</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>是温燥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>整日说书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>久坐少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>津耗气，易生内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>热。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>您开一副桑杏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，一天三服，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>也记得多喝水。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>陈皮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>柳先生，我最喜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>听您</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>啦，您真是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>啥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都知道</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>啥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都会，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>什么像什么。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>嘿嘿，小兄弟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过奖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了，我只是</t>
     </r>
     <r>
       <rPr>
@@ -270,27 +529,335 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，也不是没有</t>
+      <t>些王侯将相，才子佳人，来听</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>书的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>客官喜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>什么，我就</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>什么。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>先生您</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>在就在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这讲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一段吧。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>无妨，呵呵，那就</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王道士胡诌妒妇方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>正巧天齐庙有位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>摆摊卖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>膏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>王道士，因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>朋友问：“什么汤？怎么吃法？”</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>王一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道：“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>妒的膏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>倒没</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。有一种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汤药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，或者可医，只是慢些儿，不能立刻见效的。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>朋友道：“</t>
     </r>
     <r>
       <rPr>
@@ -310,30 +877,381 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>个可能。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>嗯，以后可别乱说啊，这小郎中真是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>…</t>
+      <t>也不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>什么。只怕未必见效。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>王一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道：“一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不效，吃十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>；今日不效，明日再吃；今年不效，明年再吃。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>“横</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竖这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>三味</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>润</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>肺开胃不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>人的，甜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丝丝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的，又止咳嗽，又好吃。吃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一百</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，人横</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>是要死的，死了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>妒什么？那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>就见效了。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>说京城有一富商，娶了位善妒的夫人，家中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鸡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>飞狗跳无一日安宁。他的朋友</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>觉得这是病，得找人医治。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>哈哈哈，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>种方子。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -342,86 +1260,160 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哇，这就是传说中的花和尚吗？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>hide</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>陈皮</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>他是花和尚，你是花痴，正好凑一对儿。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>找打！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>哎哟！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>after</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>_02</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>022治</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>疗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>成功</t>
+    <r>
+      <t>是啊是啊，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一段吧。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>人家柳先生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>病着呢，你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>别在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>胡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>哈哈哈，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的也不无道理。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -430,7 +1422,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -495,27 +1487,6 @@
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="3"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="6">
@@ -623,12 +1594,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -983,10 +1954,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -999,8 +1970,8 @@
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="5" t="s">
-        <v>30</v>
+      <c r="H2" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1018,7 +1989,7 @@
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
-      <c r="L3" s="17"/>
+      <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.4">
@@ -1038,6 +2009,7 @@
       <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
@@ -1084,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
@@ -1132,18 +2104,18 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>33</v>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1154,18 +2126,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1176,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -1184,8 +2154,8 @@
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1" t="s">
-        <v>35</v>
+      <c r="H4" s="19" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1196,18 +2166,16 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1218,16 +2186,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1" t="s">
-        <v>37</v>
+      <c r="H6" s="19" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1238,20 +2206,16 @@
         <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="19" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1261,17 +2225,17 @@
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>39</v>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>41</v>
+      <c r="H8" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1282,7 +2246,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1291,7 +2255,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1301,17 +2265,17 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>43</v>
+      <c r="C10" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1321,17 +2285,17 @@
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>39</v>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1341,28 +2305,176 @@
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>43</v>
+      <c r="C12" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/022_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/022_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702BBFB9-2329-416C-AA10-F80776A61898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402C0C4D-7512-4CA8-BE8D-3B84158DB746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3382" yWindow="3008" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -472,6 +461,784 @@
   </si>
   <si>
     <r>
+      <t>无妨，呵呵，那就</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王道士胡诌妒妇方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>正巧天齐庙有位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>摆摊卖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>膏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>王道士，因</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>朋友问：“什么汤？怎么吃法？”</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>王一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道：“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>妒的膏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>倒没</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。有一种</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汤药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，或者可医，只是慢些儿，不能立刻见效的。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>朋友道：“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>也不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>什么。只怕未必见效。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>王一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道：“一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不效，吃十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>剂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>；今日不效，明日再吃；今年不效，明年再吃。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>“横</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竖这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>三味</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>都是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>润</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>肺开胃不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>人的，甜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丝丝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的，又止咳嗽，又好吃。吃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一百</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>岁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>，人横</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>竖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>是要死的，死了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>妒什么？那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>就见效了。”</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>说京城有一富商，娶了位善妒的夫人，家中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>鸡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>飞狗跳无一日安宁。他的朋友</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>觉得这是病，得找人医治。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>哈哈哈，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>种方子。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>半夏</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>是啊是啊，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>讲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>一段吧。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>人家柳先生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>病着呢，你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>别在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>胡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>闹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>哈哈哈，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>的也不无道理。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -529,7 +1296,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>些王侯将相，才子佳人，来听</t>
+      <t>些王侯将相，才子佳人的故事，来听</t>
     </r>
     <r>
       <rPr>
@@ -595,7 +1362,7 @@
   </si>
   <si>
     <r>
-      <t>先生您</t>
+      <t>先生，您</t>
     </r>
     <r>
       <rPr>
@@ -636,784 +1403,6 @@
         <charset val="128"/>
       </rPr>
       <t>一段吧。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>无妨，呵呵，那就</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>王道士胡诌妒妇方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>正巧天齐庙有位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>摆摊卖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>膏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>王道士，因</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>膏药灵验得名王一贴，富商的朋友便去求方问药。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>朋友问：“什么汤？怎么吃法？”</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>王一贴道：“这叫做‘疗妒汤’。用极好的秋梨一个，二钱冰糖，一钱陈皮，水三碗，梨熟为度。每日清晨吃这一个梨，吃来吃去就好了。”</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>王一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>贴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>道：“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这贴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>妒的膏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>倒没</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>经过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。有一种</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>汤药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，或者可医，只是慢些儿，不能立刻见效的。”</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>朋友道：“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>也不</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>什么。只怕未必见效。”</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>王一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>贴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>道：“一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>剂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>不效，吃十</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>剂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>；今日不效，明日再吃；今年不效，明年再吃。”</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>“横</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>竖这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>三味</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>药</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>都是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>润</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>肺开胃不</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>伤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>人的，甜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>丝丝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的，又止咳嗽，又好吃。吃</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一百</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>岁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>，人横</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>竖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>是要死的，死了</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>妒什么？那</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>就见效了。”</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>说京城有一富商，娶了位善妒的夫人，家中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>鸡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>飞狗跳无一日安宁。他的朋友</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>觉得这是病，得找人医治。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>哈哈哈，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>种方子。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>半夏</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>是啊是啊，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>讲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>一段吧。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>人家柳先生</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>还</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>病着呢，你</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>们</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>别在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>胡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>闹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>哈哈哈，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>道士</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>的也不无道理。</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -1422,11 +1411,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1440,7 +1429,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1461,7 +1450,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1603,7 +1592,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1882,27 +1871,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1952,7 +1941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>31</v>
       </c>
@@ -1986,66 +1975,66 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="14"/>
       <c r="L3" s="18"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="C6" s="10"/>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="C7" s="10"/>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="C8" s="10"/>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -2057,20 +2046,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -2096,7 +2085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2118,7 +2107,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2138,7 +2127,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2158,7 +2147,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2178,7 +2167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2195,10 +2184,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2215,10 +2204,10 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2226,7 +2215,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
@@ -2235,10 +2224,10 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2255,10 +2244,10 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2275,10 +2264,10 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2295,10 +2284,10 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2315,10 +2304,10 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2335,10 +2324,10 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2355,10 +2344,10 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2375,10 +2364,10 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2395,10 +2384,10 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2415,10 +2404,10 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2435,10 +2424,10 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2455,11 +2444,13 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
@@ -2473,7 +2464,7 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/022_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/022_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402C0C4D-7512-4CA8-BE8D-3B84158DB746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EA4C4B-E9F9-453E-B8E6-0B01BB6C0B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3382" yWindow="3008" windowWidth="21601" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="57">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>LineIndex</t>
   </si>
@@ -69,68 +66,18 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>clinic</t>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>current_scene</t>
   </si>
   <si>
-    <t>story_npc_cured</t>
-  </si>
-  <si>
     <r>
       <t>022治</t>
     </r>
@@ -1405,13 +1352,101 @@
       <t>一段吧。</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>cured</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1463,22 +1498,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1493,20 +1542,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1537,7 +1588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1563,24 +1614,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1589,6 +1629,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1870,175 +1938,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="22" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="22" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="M2" s="23"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="C6" s="10"/>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="C7" s="10"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="C8" s="10"/>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="14"/>
+      <c r="T2" s="24"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="11"/>
+      <c r="L3" s="13"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="9"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="9"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="C8" s="9"/>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="11"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="14"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="14"/>
+      <c r="H18" s="11"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="14"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="14"/>
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{A60CFCD5-67B4-4E81-B0F8-412E481358F7}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{5CBEC3F8-934E-4FC8-BE8E-338F6EEB2209}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{CE7AEC35-0AE6-4E6D-8379-188B3BA48D66}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{CC24C4F9-43E6-4B88-B069-9A2D6690AFAB}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{1048F070-7A0A-48F4-8CE7-A59C017A27BD}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2061,28 +2156,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2090,21 +2185,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2112,19 +2207,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2132,19 +2227,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="19" t="s">
-        <v>37</v>
+      <c r="H4" s="14" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2152,19 +2247,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2172,19 +2267,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="19" t="s">
-        <v>55</v>
+      <c r="H6" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2192,19 +2287,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2212,19 +2307,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="4" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2232,19 +2327,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2252,19 +2347,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2272,19 +2367,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2292,19 +2387,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2312,19 +2407,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2332,19 +2427,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2352,19 +2447,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2372,19 +2467,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2392,19 +2487,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2412,19 +2507,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2432,19 +2527,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2452,19 +2547,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/022_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/022_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EA4C4B-E9F9-453E-B8E6-0B01BB6C0B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2185BE9-F869-45B3-BFB5-0D7D7E963DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="62">
   <si>
     <t>LineIndex</t>
   </si>
@@ -1440,6 +1451,10 @@
   </si>
   <si>
     <t>cured</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
   </si>
 </sst>
 </file>
@@ -1450,7 +1465,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1464,7 +1479,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1485,7 +1500,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1588,7 +1603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1658,9 +1673,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1939,25 +1957,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>42</v>
       </c>
@@ -2019,7 +2037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1">
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
@@ -2140,21 +2158,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2179,8 +2197,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2201,8 +2222,9 @@
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2221,8 +2243,9 @@
       <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2241,8 +2264,9 @@
       <c r="H4" s="14" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2261,8 +2285,9 @@
       <c r="H5" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2281,8 +2306,9 @@
       <c r="H6" s="14" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2301,8 +2327,9 @@
       <c r="H7" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2321,8 +2348,9 @@
       <c r="H8" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2341,8 +2369,9 @@
       <c r="H9" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2361,8 +2390,9 @@
       <c r="H10" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2381,8 +2411,9 @@
       <c r="H11" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -2401,8 +2432,9 @@
       <c r="H12" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2421,8 +2453,9 @@
       <c r="H13" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2441,8 +2474,9 @@
       <c r="H14" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2461,8 +2495,9 @@
       <c r="H15" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2481,8 +2516,9 @@
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2501,8 +2537,9 @@
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2521,8 +2558,9 @@
       <c r="H18" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2541,8 +2579,9 @@
       <c r="H19" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2561,6 +2600,7 @@
       <c r="H20" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
